--- a/bases_de_dados/Entrada - Contagem de Empresas.xlsx
+++ b/bases_de_dados/Entrada - Contagem de Empresas.xlsx
@@ -1,14 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abymael\Documents\Capacita\Imersão\Treinos\Projeto\bases_de_dados\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E7543A6-3E9E-4C6F-ABF6-CE475B289456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Propostas Submetidas" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Empresas" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="Graduação" sheetId="3" r:id="rId6"/>
+    <sheet name="Propostas Submetidas" sheetId="1" r:id="rId1"/>
+    <sheet name="Empresas" sheetId="2" r:id="rId2"/>
+    <sheet name="Graduação" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -108,37 +117,48 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="5">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -152,27 +172,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -182,67 +209,53 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -432,535 +445,539 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="5" max="6" width="14.75"/>
+    <col min="5" max="6" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="D3" s="9">
-        <v>4.0</v>
-      </c>
-      <c r="E3" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B10" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B11" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="C11" s="9">
-        <v>19.0</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B12" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B13" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B14" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C15" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B16" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B17" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B18" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B19" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B20" s="6">
-        <v>6.0</v>
-      </c>
-      <c r="C20" s="9">
-        <v>17.0</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B21" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="9">
-        <v>9.0</v>
-      </c>
-      <c r="E21" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="F21" s="9">
-        <v>2.0</v>
-      </c>
-      <c r="G21" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B22" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B23" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="9">
-        <v>1.0</v>
-      </c>
-      <c r="H23" s="9">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="9">
-        <v>2025.0</v>
-      </c>
-      <c r="B25" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B26" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12"/>
-      <c r="B27" s="12"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12"/>
-      <c r="B28" s="12"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>19</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2">
+        <v>11</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>3</v>
+      </c>
+      <c r="E15" s="5">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
+      </c>
+      <c r="C20" s="5">
+        <v>17</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5">
+        <v>9</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2</v>
+      </c>
+      <c r="F21" s="5">
+        <v>2</v>
+      </c>
+      <c r="G21" s="5">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="2">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="2">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="2">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>12</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C1:H1"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="3" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="3" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="5"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="10"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="2"/>
@@ -971,12 +988,12 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>2.0</v>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -996,12 +1013,12 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3.0</v>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1021,12 +1038,12 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>4.0</v>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1046,12 +1063,12 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>5.0</v>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1071,12 +1088,12 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6.0</v>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1087,7 +1104,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="M8" s="2"/>
@@ -1098,12 +1115,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7.0</v>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1123,12 +1140,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B10" s="6">
-        <v>8.0</v>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2">
+        <v>8</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1140,7 +1157,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N10" s="2"/>
@@ -1150,12 +1167,12 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B11" s="6">
-        <v>9.0</v>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1175,26 +1192,26 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B12" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="C12" s="6" t="s">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H12" s="2"/>
@@ -1210,12 +1227,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B13" s="6">
-        <v>11.0</v>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2">
+        <v>11</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1235,12 +1252,12 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B14" s="6">
-        <v>12.0</v>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1260,20 +1277,20 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C15" s="6" t="s">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="2"/>
@@ -1282,10 +1299,10 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N15" s="2"/>
@@ -1295,12 +1312,12 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B16" s="6">
-        <v>2.0</v>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1320,12 +1337,12 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B17" s="6">
-        <v>3.0</v>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1345,12 +1362,12 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B18" s="6">
-        <v>4.0</v>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1370,12 +1387,12 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B19" s="6">
-        <v>5.0</v>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1395,12 +1412,12 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B20" s="6">
-        <v>6.0</v>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1420,57 +1437,57 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B21" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C21" s="6" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6" t="s">
+      <c r="L21" s="2"/>
+      <c r="M21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="6"/>
+      <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B22" s="6">
-        <v>8.0</v>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="2">
+        <v>8</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1485,19 +1502,19 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="6" t="s">
+      <c r="P22" s="2" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23">
-      <c r="A23" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B23" s="6">
-        <v>9.0</v>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="2">
+        <v>9</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1512,19 +1529,19 @@
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
-      <c r="P23" s="6" t="s">
+      <c r="P23" s="2" t="s">
         <v>29</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24">
-      <c r="A24" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10.0</v>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="2">
+        <v>10</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -1539,17 +1556,17 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="6"/>
+      <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25">
-      <c r="A25" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B25" s="6">
-        <v>11.0</v>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -1569,12 +1586,12 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B26" s="6">
-        <v>12.0</v>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>12</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -1594,8 +1611,8 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27">
-      <c r="A27" s="12"/>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1604,88 +1621,89 @@
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S27"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="10"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A2" s="2"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="3" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="3" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="10"/>
+      <c r="P2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="5"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="10"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1694,23 +1712,23 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4">
-      <c r="A4" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B4" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="C4" s="6" t="s">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="2"/>
@@ -1727,12 +1745,12 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5">
-      <c r="A5" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B5" s="6">
-        <v>3.0</v>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1752,12 +1770,12 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6">
-      <c r="A6" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B6" s="6">
-        <v>4.0</v>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1777,12 +1795,12 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7">
-      <c r="A7" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B7" s="6">
-        <v>5.0</v>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2">
+        <v>5</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1802,12 +1820,12 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8">
-      <c r="A8" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6.0</v>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2">
+        <v>6</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1818,7 +1836,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="6"/>
+      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1827,12 +1845,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B9" s="6">
-        <v>7.0</v>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2">
+        <v>7</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1852,12 +1870,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B10" s="6">
-        <v>8.0</v>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2">
+        <v>8</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1869,7 +1887,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="6"/>
+      <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1877,12 +1895,12 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B11" s="6">
-        <v>9.0</v>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2">
+        <v>9</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1902,18 +1920,18 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B12" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1927,12 +1945,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B13" s="6">
-        <v>11.0</v>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2">
+        <v>11</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1952,12 +1970,12 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <v>2024.0</v>
-      </c>
-      <c r="B14" s="6">
-        <v>12.0</v>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2">
+        <v>12</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1977,24 +1995,24 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B15" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -2002,12 +2020,12 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B16" s="6">
-        <v>2.0</v>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="2">
+        <v>2</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -2027,12 +2045,12 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17">
-      <c r="A17" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B17" s="6">
-        <v>3.0</v>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -2052,20 +2070,20 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18">
-      <c r="A18" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B18" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="C18" s="6" t="s">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="2"/>
@@ -2083,12 +2101,12 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19">
-      <c r="A19" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B19" s="6">
-        <v>5.0</v>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -2108,12 +2126,12 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20">
-      <c r="A20" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B20" s="6">
-        <v>6.0</v>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="2">
+        <v>6</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -2133,26 +2151,26 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21">
-      <c r="A21" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B21" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6" t="s">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="2">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M21" s="6"/>
+      <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -2160,12 +2178,12 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22">
-      <c r="A22" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B22" s="6">
-        <v>8.0</v>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="2">
+        <v>8</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -2185,12 +2203,12 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23">
-      <c r="A23" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B23" s="6">
-        <v>9.0</v>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="2">
+        <v>9</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -2210,12 +2228,12 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24">
-      <c r="A24" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B24" s="6">
-        <v>10.0</v>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="2">
+        <v>10</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -2235,12 +2253,12 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25">
-      <c r="A25" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B25" s="6">
-        <v>11.0</v>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="2">
+        <v>11</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
@@ -2260,12 +2278,12 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26">
-      <c r="A26" s="6">
-        <v>2025.0</v>
-      </c>
-      <c r="B26" s="6">
-        <v>12.0</v>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="2">
+        <v>12</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -2285,8 +2303,8 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27">
-      <c r="A27" s="12"/>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2295,6 +2313,6 @@
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:S2"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>